--- a/tests/Import/fixtures/28_celda_multilinea_en_los_datos.xlsx
+++ b/tests/Import/fixtures/28_celda_multilinea_en_los_datos.xlsx
@@ -56,7 +56,7 @@
     <t>ML-03</t>
   </si>
   <si>
-    <t>ARTICULO MULTILINEA FILA 03</t>
+    <t>PERFIL ALUMINIO 20x20 \</t>
   </si>
   <si>
     <t>7794280000004</t>
